--- a/divi5/seo-data/MedTech_SEO_Data.xlsx
+++ b/divi5/seo-data/MedTech_SEO_Data.xlsx
@@ -85,9 +85,7 @@
   </cellStyleXfs>
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
@@ -627,7 +625,8 @@
       <c r="D7" s="3" t="inlineStr">
         <is>
           <t>{"@context":"https://schema.org","@type":"Service","name":"Real-Time IVF Lab Monitoring","serviceType":"Healthcare Technology","provider":{"@type":"Organization","@id":"/#organization","name":"MedTech For Solutions","url":"/","telephone":"+1-866-634-9144"},"url":"/services/lab-solutions/real-time-monitoring/","description":"Monitor your IVF laboratory in real time with MedTech's OvaTools platform. Track incubators, cryogenic tanks, patient cycles, and equipment with instant alerts, compliance reporting, and 24/7 oversight for fertility clinics.","areaServed":{"@type":"Country","name":"United States"}}
-{"@context":"https://schema.org","@type":"BreadcrumbList","itemListElement":[{"@type":"ListItem","position":1,"name":"Home","item":"/"},{"@type":"ListItem","position":2,"name":"Laboratory Solutions","item":"/services/lab-solutions/"},{"@type":"ListItem","position":3,"name":"Real-Time Monitoring","item":"/services/lab-solutions/real-time-monitoring/"}]}</t>
+{"@context":"https://schema.org","@type":"BreadcrumbList","itemListElement":[{"@type":"ListItem","position":1,"name":"Home","item":"/"},{"@type":"ListItem","position":2,"name":"Laboratory Solutions","item":"/services/lab-solutions/"},{"@type":"ListItem","position":3,"name":"Real-Time Monitoring","item":"/services/lab-solutions/real-time-monitoring/"}]}
+{"@context":"https://schema.org","@type":"FAQPage","mainEntity":[{"@type":"Question","name":"What equipment can be monitored?","acceptedAnswer":{"@type":"Answer","text":"Incubators, cryogenic storage tanks, refrigerators, and any critical lab equipment &amp;mdash; tracking temperature, CO2, humidity, and other parameters around the clock."}},{"@type":"Question","name":"How fast do alerts arrive?","acceptedAnswer":{"@type":"Answer","text":"Alert response is under two seconds, delivered simultaneously by SMS, email, and in-app notification, with configurable thresholds and escalation paths for your team."}},{"@type":"Question","name":"Does the platform help with inspections and accreditation?","acceptedAnswer":{"@type":"Answer","text":"Yes. OvaTools automatically generates regulatory-ready documentation, complete audit trails, and compliance reports that support FDA, CLIA, CAP, and AABB readiness."}},{"@type":"Question","name":"Can I check my lab remotely?","acceptedAnswer":{"@type":"Answer","text":"Yes. Dashboards are securely cloud-based, so laboratory directors can review live equipment status, patient-cycle tracking, and quality metrics from anywhere."}}]}</t>
         </is>
       </c>
     </row>
@@ -742,7 +741,8 @@
       <c r="D12" s="3" t="inlineStr">
         <is>
           <t>{"@context":"https://schema.org","@type":"Service","name":"Fertility Practice Management Services","serviceType":"Healthcare Practice Management","provider":{"@type":"Organization","@id":"/#organization","name":"MedTech For Solutions","url":"/","telephone":"+1-866-634-9144"},"url":"/services/management-services/","description":"Comprehensive fertility practice management services from MedTech For Solutions: data-driven marketing, dedicated call center operations, accounting and financial oversight, human resources management, and professional liability insurance and risk management.","areaServed":{"@type":"Country","name":"United States"},"hasOfferCatalog":{"@type":"OfferCatalog","name":"Management Services","itemListElement":[{"@type":"Offer","itemOffered":{"@type":"Service","name":"Marketing","url":"/services/management-services/marketing/"}},{"@type":"Offer","itemOffered":{"@type":"Service","name":"Call Center","url":"/services/management-services/call-center/"}},{"@type":"Offer","itemOffered":{"@type":"Service","name":"Accounting &amp; Finance","url":"/services/management-services/accounting-finance/"}},{"@type":"Offer","itemOffered":{"@type":"Service","name":"Human Resources","url":"/services/management-services/human-resources/"}},{"@type":"Offer","itemOffered":{"@type":"Service","name":"Insurance &amp; Risk Management","url":"/services/management-services/insurance-risk-management/"}}]}}
-{"@context":"https://schema.org","@type":"BreadcrumbList","itemListElement":[{"@type":"ListItem","position":1,"name":"Home","item":"/"},{"@type":"ListItem","position":2,"name":"Management Services","item":"/services/management-services/"}]}</t>
+{"@context":"https://schema.org","@type":"BreadcrumbList","itemListElement":[{"@type":"ListItem","position":1,"name":"Home","item":"/"},{"@type":"ListItem","position":2,"name":"Management Services","item":"/services/management-services/"}]}
+{"@context":"https://schema.org","@type":"FAQPage","mainEntity":[{"@type":"Question","name":"Can we start with just one service?","acceptedAnswer":{"@type":"Answer","text":"Absolutely. Many practices begin with a single service line &amp;mdash; often the call center or accounting &amp;mdash; and expand as results build. Every plan is scoped to what your practice actually needs."}},{"@type":"Question","name":"How are engagements priced?","acceptedAnswer":{"@type":"Answer","text":"Each solution is scoped individually after a free consultation, based on your practice&amp;rsquo;s size, goals, and the services involved. You&amp;rsquo;ll always know the plan before anything begins."}},{"@type":"Question","name":"How quickly can we get started?","acceptedAnswer":{"@type":"Answer","text":"We respond to every inquiry within one business day, and most engagements begin with an operational assessment scheduled within the first conversation."}}]}</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,8 @@
       <c r="D14" s="3" t="inlineStr">
         <is>
           <t>{"@context":"https://schema.org","@type":"Service","name":"Fertility Clinic Call Center &amp; Patient Communication","serviceType":"Call Center Services","provider":{"@type":"Organization","@id":"/#organization","name":"MedTech For Solutions","url":"/","telephone":"+1-866-634-9144"},"url":"/services/management-services/call-center/","description":"Dedicated call center solutions for fertility clinics: professional patient scheduling, empathetic inquiry handling, and communication management."}
-{"@context":"https://schema.org","@type":"BreadcrumbList","itemListElement":[{"@type":"ListItem","position":1,"name":"Home","item":"/"},{"@type":"ListItem","position":2,"name":"Management Services","item":"/services/management-services/"},{"@type":"ListItem","position":3,"name":"Call Center","item":"/services/management-services/call-center/"}]}</t>
+{"@context":"https://schema.org","@type":"BreadcrumbList","itemListElement":[{"@type":"ListItem","position":1,"name":"Home","item":"/"},{"@type":"ListItem","position":2,"name":"Management Services","item":"/services/management-services/"},{"@type":"ListItem","position":3,"name":"Call Center","item":"/services/management-services/call-center/"}]}
+{"@context":"https://schema.org","@type":"FAQPage","mainEntity":[{"@type":"Question","name":"Are your call agents trained specifically for fertility patients?","acceptedAnswer":{"@type":"Answer","text":"Yes. Every agent completes fertility-specific call training and protocols before taking a single call. They understand the emotional weight of reproductive medicine inquiries and handle each conversation with empathy, discretion, and clinical accuracy. Bilingual support is available."}},{"@type":"Question","name":"Do you provide after-hours and overflow coverage?","acceptedAnswer":{"@type":"Answer","text":"Yes. Coverage is available 24/7, including overflow support during your front desk&amp;rsquo;s peak hours and full after-hours answering, so no patient call ever goes unanswered."}},{"@type":"Question","name":"Can you work within our existing scheduling workflows?","acceptedAnswer":{"@type":"Answer","text":"Yes. We build call protocols around your practice&amp;rsquo;s scheduling systems and provider calendars, optimizing appointment slots, reducing no-shows, and matching each patient with the right specialist."}},{"@type":"Question","name":"How is patient information protected?","acceptedAnswer":{"@type":"Answer","text":"All communication is handled through HIPAA-aware processes covering phone, email, patient-portal, and text channels, with documented protocols for verification and secure information handling."}}]}</t>
         </is>
       </c>
     </row>
@@ -834,7 +835,8 @@
       <c r="D16" s="3" t="inlineStr">
         <is>
           <t>{"@context":"https://schema.org","@type":"Service","name":"Human Resources for Fertility Practices","serviceType":"Healthcare HR Services","provider":{"@type":"Organization","@id":"/#organization","name":"MedTech For Solutions","url":"/","telephone":"+1-866-634-9144"},"url":"/services/management-services/human-resources/","description":"Recruitment, onboarding, performance management, and HR compliance services to support fertility clinic workforce needs."}
-{"@context":"https://schema.org","@type":"BreadcrumbList","itemListElement":[{"@type":"ListItem","position":1,"name":"Home","item":"/"},{"@type":"ListItem","position":2,"name":"Management Services","item":"/services/management-services/"},{"@type":"ListItem","position":3,"name":"Human Resources","item":"/services/management-services/human-resources/"}]}</t>
+{"@context":"https://schema.org","@type":"BreadcrumbList","itemListElement":[{"@type":"ListItem","position":1,"name":"Home","item":"/"},{"@type":"ListItem","position":2,"name":"Management Services","item":"/services/management-services/"},{"@type":"ListItem","position":3,"name":"Human Resources","item":"/services/management-services/human-resources/"}]}
+{"@context":"https://schema.org","@type":"FAQPage","mainEntity":[{"@type":"Question","name":"Which roles can you recruit for?","acceptedAnswer":{"@type":"Answer","text":"Both clinical and administrative positions &amp;mdash; embryologists, nurses, front-desk staff, practice managers, and more &amp;mdash; using healthcare-specific job descriptions, credentialing, and background verification."}},{"@type":"Question","name":"Do you handle healthcare compliance training?","acceptedAnswer":{"@type":"Answer","text":"Yes. We deliver OSHA and HIPAA training programs, develop employee handbooks and policies, and monitor healthcare-specific employment regulations on an ongoing basis."}},{"@type":"Question","name":"Can you support a small or growing practice?","acceptedAnswer":{"@type":"Answer","text":"Yes. Our HR services scale to your practice&amp;rsquo;s size and stage &amp;mdash; from building your first handbook to managing the complete employee lifecycle across multiple locations."}},{"@type":"Question","name":"What does your onboarding program include?","acceptedAnswer":{"@type":"Answer","text":"Structured onboarding covers credentialing and background verification, regulatory training completion, benefits enrollment, and team-integration milestones that accelerate new-hire productivity."}}]}</t>
         </is>
       </c>
     </row>
@@ -984,10 +986,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A13"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="100" customWidth="1" min="1" max="1"/>
+    <col width="110" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1003,69 +1005,28 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>This workbook is the single source for the SEO metadata that was removed from the</t>
+          <t>Meta Title / Meta Description: enter in the SEO plugin (or OTTO) per page.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Divi Code module HTML files during performance optimization.</t>
+          <t>Schema Markup Code: paste each JSON-LD object wrapped in &lt;script type="application/ld+json"&gt;...&lt;/script&gt;, or deploy via OTTO.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr"/>
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>FAQPage schema on call-center, human-resources, real-time-monitoring, and management-services reflects the on-page FAQ sections.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Where to re-enter each column in WordPress:</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> - Meta Title / Meta Description: the SEO plugin (or OTTO / Search Atlas) per page.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> - Schema Markup Code: paste each JSON-LD object into the SEO plugin schema field</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   wrapped in &lt;script type="application/ld+json"&gt;...&lt;/script&gt;, or let OTTO deploy it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>Multiple schema objects for one page are separated by line breaks in column D.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>URLs are root-relative paths (domain-agnostic, per client direction).</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>Extracted from the static site source on 2026-07-21.</t>
+          <t>URLs are root-relative paths. Extracted 2026-07-21.</t>
         </is>
       </c>
     </row>
